--- a/data/trans_camb/P43B-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P43B-Estudios-trans_camb.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-0,34</t>
+          <t>-0,44</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,34</t>
+          <t>-0,44</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 1,42</t>
+          <t>-3,16; 1,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 2,52</t>
+          <t>-2,69; 2,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 1,42</t>
+          <t>-3,16; 1,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 2,52</t>
+          <t>-2,69; 2,07</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-6,6%</t>
+          <t>-8,65%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-6,6%</t>
+          <t>-8,65%</t>
         </is>
       </c>
     </row>
@@ -657,22 +657,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-51,2; 36,28</t>
+          <t>-49,59; 40,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-44,97; 63,05</t>
+          <t>-43,77; 51,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-51,2; 36,28</t>
+          <t>-49,59; 40,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-44,97; 63,05</t>
+          <t>-43,77; 51,53</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-7,45</t>
+          <t>-3,11</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-7,45</t>
+          <t>-3,11</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,88; -4,9</t>
+          <t>-13,12; -5,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,39; -2,39</t>
+          <t>-7,24; 0,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,88; -4,9</t>
+          <t>-13,12; -5,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-15,39; -2,39</t>
+          <t>-7,24; 0,61</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-39,52%</t>
+          <t>-16,5%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-39,52%</t>
+          <t>-16,5%</t>
         </is>
       </c>
     </row>
@@ -773,22 +773,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-60,02; -28,04</t>
+          <t>-60,75; -30,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-71,08; -14,59</t>
+          <t>-33,75; 3,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-60,02; -28,04</t>
+          <t>-60,75; -30,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-71,08; -14,59</t>
+          <t>-33,75; 3,65</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,14</t>
+          <t>0,4</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,14</t>
+          <t>0,4</t>
         </is>
       </c>
     </row>
@@ -833,22 +833,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,59; 6,57</t>
+          <t>-14,41; 7,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 11,32</t>
+          <t>-10,94; 9,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-15,59; 6,57</t>
+          <t>-14,41; 7,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 11,32</t>
+          <t>-10,94; 9,89</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -889,22 +889,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-29,73; 17,38</t>
+          <t>-29,03; 18,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-16,66; 31,9</t>
+          <t>-20,58; 26,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-29,73; 17,38</t>
+          <t>-29,03; 18,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-16,66; 31,9</t>
+          <t>-20,58; 26,51</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,18</t>
+          <t>4,07</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,18</t>
+          <t>4,07</t>
         </is>
       </c>
     </row>
@@ -949,22 +949,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 0,38</t>
+          <t>-4,77; 0,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 4,71</t>
+          <t>1,53; 6,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 0,38</t>
+          <t>-4,77; 0,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 4,71</t>
+          <t>1,53; 6,48</t>
         </is>
       </c>
     </row>
@@ -982,7 +982,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>28,41%</t>
         </is>
       </c>
     </row>
@@ -1005,22 +1005,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-29,02; 2,88</t>
+          <t>-30,44; 1,37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-30,16; 35,11</t>
+          <t>9,37; 50,81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-29,02; 2,88</t>
+          <t>-30,44; 1,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-30,16; 35,11</t>
+          <t>9,37; 50,81</t>
         </is>
       </c>
     </row>
